--- a/grupos/4ARHV - Estadisticos 20232.xlsx
+++ b/grupos/4ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="62">
   <si>
     <t>Materia</t>
   </si>
@@ -200,19 +200,10 @@
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>CHONKOA</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>SANDOVAL</t>
-  </si>
-  <si>
     <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>ABRIL</t>
   </si>
 </sst>
 </file>
@@ -720,22 +711,22 @@
         <v>5</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -797,22 +788,22 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -833,22 +824,22 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
+        <v>7</v>
+      </c>
+      <c r="V5">
+        <v>8</v>
+      </c>
+      <c r="W5">
+        <v>5</v>
+      </c>
+      <c r="X5">
         <v>6</v>
       </c>
-      <c r="V5">
-        <v>7</v>
-      </c>
-      <c r="W5">
+      <c r="Y5">
         <v>6</v>
-      </c>
-      <c r="X5">
-        <v>5</v>
-      </c>
-      <c r="Y5">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -874,22 +865,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -913,7 +904,7 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -951,22 +942,22 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1028,22 +1019,22 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1064,22 +1055,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1105,22 +1096,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1147,13 +1138,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1182,22 +1173,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1218,19 +1209,19 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>8</v>
@@ -1259,22 +1250,22 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1304,7 +1295,7 @@
         <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1336,22 +1327,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1372,22 +1363,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1413,22 +1404,22 @@
         <v>10</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1452,13 +1443,13 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>10</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1490,22 +1481,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1526,10 +1517,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1538,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1567,22 +1558,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1606,16 +1597,16 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1644,22 +1635,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1683,7 +1674,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1721,22 +1712,22 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1760,13 +1751,13 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -1798,22 +1789,22 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1834,16 +1825,16 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -1875,22 +1866,22 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1911,19 +1902,19 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
         <v>8</v>
@@ -1952,22 +1943,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -1988,19 +1979,19 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2029,22 +2020,22 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2068,7 +2059,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2077,7 +2068,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2106,22 +2097,22 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2151,7 +2142,7 @@
         <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>10</v>
@@ -2183,22 +2174,22 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2260,22 +2251,22 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2296,7 +2287,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2308,7 +2299,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2337,22 +2328,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2385,7 +2376,7 @@
         <v>10</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2414,22 +2405,22 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2453,13 +2444,13 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2491,22 +2482,22 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2536,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2568,22 +2559,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2613,13 +2604,13 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2755,40 +2746,40 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>84.2</v>
+        <v>83.3</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L4">
-        <v>75</v>
+        <v>36.6</v>
       </c>
       <c r="M4">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
       <c r="N4">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>84.2</v>
+        <v>83.3</v>
       </c>
       <c r="Q4">
-        <v>20</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R4">
-        <v>75</v>
+        <v>36.6</v>
       </c>
       <c r="S4">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2814,37 +2805,37 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="I5">
         <v>100</v>
       </c>
       <c r="J5">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>91.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2873,7 +2864,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I6">
         <v>100</v>
@@ -2891,7 +2882,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2932,7 +2923,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -2950,7 +2941,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -2991,40 +2982,40 @@
         <v>81.3</v>
       </c>
       <c r="H8">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I8">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="K8">
-        <v>92</v>
+        <v>94.2</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="N8">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O8">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="Q8">
-        <v>92</v>
+        <v>94.2</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3050,40 +3041,40 @@
         <v>81.3</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="I9">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="O9">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S9">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3109,37 +3100,37 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I10">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J10">
         <v>100</v>
       </c>
       <c r="K10">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O10">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3168,7 +3159,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -3186,7 +3177,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3230,37 +3221,37 @@
         <v>85.7</v>
       </c>
       <c r="I12">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J12">
-        <v>84.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K12">
-        <v>70</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N12">
         <v>85.7</v>
       </c>
       <c r="O12">
-        <v>91.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="P12">
-        <v>84.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>70</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3348,7 +3339,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3366,7 +3357,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3404,16 +3395,16 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="I15">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>98</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3422,16 +3413,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>97.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O15">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3463,7 +3454,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3481,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3522,7 +3513,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -3540,7 +3531,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3581,16 +3572,16 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="L18">
         <v>100</v>
@@ -3599,16 +3590,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -3640,40 +3631,40 @@
         <v>81.3</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I19">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M19">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S19">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3711,7 +3702,7 @@
         <v>100</v>
       </c>
       <c r="L20">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -3729,7 +3720,7 @@
         <v>100</v>
       </c>
       <c r="R20">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3758,16 +3749,16 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="I21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J21">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="K21">
-        <v>96</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -3776,16 +3767,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P21">
-        <v>94.7</v>
+        <v>97.2</v>
       </c>
       <c r="Q21">
-        <v>96</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3826,10 +3817,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -3844,10 +3835,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R22">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -3876,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I23">
         <v>100</v>
@@ -3885,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>94</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -3894,7 +3885,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -3903,7 +3894,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>94</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -3935,37 +3926,37 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>97.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I24">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="K24">
-        <v>92</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>97.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O24">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="Q24">
-        <v>92</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4003,10 +3994,10 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4021,10 +4012,10 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4053,7 +4044,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I26">
         <v>100</v>
@@ -4071,7 +4062,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4112,7 +4103,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4130,7 +4121,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4171,16 +4162,16 @@
         <v>100</v>
       </c>
       <c r="H28">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I28">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4189,16 +4180,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O28">
-        <v>95.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>92</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4270,19 +4261,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4302,16 +4293,16 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G3" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>8.800000000000001</v>
@@ -4334,19 +4325,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G4" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4366,16 +4357,16 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G5" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>
@@ -4398,16 +4389,16 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G6" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -4430,19 +4421,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G7" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4492,7 +4483,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4530,87 +4521,18 @@
         <v>59</v>
       </c>
       <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
         <v>61</v>
       </c>
-      <c r="D2" t="s">
-        <v>63</v>
-      </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920205</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920393</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920393</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ARHV - Estadisticos 20232.xlsx
+++ b/grupos/4ARHV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="59">
   <si>
     <t>Materia</t>
   </si>
@@ -167,18 +167,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez López Miguel Ángel</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Urias Morales Alejandra</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Martínez López Miguel Ángel</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Urias Morales Alejandra</t>
-  </si>
-  <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
@@ -195,15 +195,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
   </si>
 </sst>
 </file>
@@ -729,22 +720,22 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -806,37 +797,37 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -883,28 +874,28 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>10</v>
@@ -960,22 +951,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1037,22 +1028,22 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1070,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1114,22 +1105,22 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1147,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1191,22 +1182,22 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1215,7 +1206,7 @@
         <v>7</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1268,25 +1259,25 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1301,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1345,40 +1336,40 @@
         <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>8</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1422,28 +1413,28 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V13">
         <v>10</v>
@@ -1499,28 +1490,28 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>8</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>10</v>
@@ -1529,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1576,28 +1567,28 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -1609,7 +1600,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1653,28 +1644,28 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>10</v>
@@ -1730,28 +1721,28 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -1763,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1807,25 +1798,25 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -1834,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1884,40 +1875,40 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1961,22 +1952,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -1994,7 +1985,7 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2038,28 +2029,28 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2068,10 +2059,10 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2115,28 +2106,28 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>10</v>
@@ -2148,7 +2139,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2192,28 +2183,28 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>10</v>
@@ -2225,7 +2216,7 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2269,37 +2260,37 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24">
         <v>8</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2346,25 +2337,25 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2379,7 +2370,7 @@
         <v>9</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2423,28 +2414,28 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2500,22 +2491,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2577,25 +2568,25 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2764,22 +2755,22 @@
         <v>6.3</v>
       </c>
       <c r="N4">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>83.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="Q4">
-        <v>9.699999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="R4">
-        <v>36.6</v>
+        <v>23.8</v>
       </c>
       <c r="S4">
-        <v>6.3</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2823,19 +2814,19 @@
         <v>100</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O5">
         <v>100</v>
       </c>
       <c r="P5">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="Q5">
-        <v>82.5</v>
+        <v>88.8</v>
       </c>
       <c r="R5">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -2882,7 +2873,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O6">
         <v>100</v>
@@ -2941,7 +2932,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -3000,22 +2991,22 @@
         <v>87.5</v>
       </c>
       <c r="N8">
-        <v>95.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O8">
-        <v>95.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="P8">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="Q8">
-        <v>94.2</v>
+        <v>96.3</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3059,22 +3050,22 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N9">
-        <v>95.7</v>
+        <v>97.3</v>
       </c>
       <c r="O9">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>96.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S9">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3118,19 +3109,19 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>92.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="O10">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P10">
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>96.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R10">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3177,7 +3168,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -3236,22 +3227,22 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N12">
-        <v>85.7</v>
+        <v>84.8</v>
       </c>
       <c r="O12">
-        <v>93.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="P12">
-        <v>86.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q12">
-        <v>80.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="R12">
-        <v>95.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="S12">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3357,7 +3348,7 @@
         <v>100</v>
       </c>
       <c r="O14">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P14">
         <v>100</v>
@@ -3413,16 +3404,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>95.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O15">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -3472,7 +3463,7 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3481,7 +3472,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -3531,7 +3522,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3590,16 +3581,16 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O18">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P18">
+        <v>95.7</v>
+      </c>
+      <c r="Q18">
         <v>94.40000000000001</v>
-      </c>
-      <c r="Q18">
-        <v>95.09999999999999</v>
       </c>
       <c r="R18">
         <v>100</v>
@@ -3649,22 +3640,22 @@
         <v>90.59999999999999</v>
       </c>
       <c r="N19">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O19">
-        <v>97.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="Q19">
-        <v>99</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R19">
-        <v>97.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S19">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3708,19 +3699,19 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -3767,16 +3758,16 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>95.7</v>
+        <v>97.3</v>
       </c>
       <c r="O21">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P21">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="Q21">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -3826,7 +3817,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -3835,10 +3826,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>99</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R22">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -3885,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -3894,10 +3885,10 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>97.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="R23">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -3944,19 +3935,19 @@
         <v>100</v>
       </c>
       <c r="N24">
-        <v>91.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="O24">
-        <v>95.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P24">
-        <v>97.2</v>
+        <v>97.8</v>
       </c>
       <c r="Q24">
-        <v>87.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R24">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4003,7 +3994,7 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>94.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O25">
         <v>100</v>
@@ -4012,10 +4003,10 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>96.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="R25">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4062,7 +4053,7 @@
         <v>100</v>
       </c>
       <c r="N26">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -4121,7 +4112,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>98.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4180,16 +4171,16 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="O28">
-        <v>97.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>96.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4252,7 +4243,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>49</v>
@@ -4261,19 +4252,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G2" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4284,7 +4275,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>50</v>
@@ -4305,7 +4296,7 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4316,7 +4307,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -4337,7 +4328,7 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4348,7 +4339,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>52</v>
@@ -4369,7 +4360,7 @@
         <v>4</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4401,7 +4392,7 @@
         <v>4</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4433,7 +4424,7 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4483,7 +4474,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4513,29 +4504,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920205</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
